--- a/data/trans_bre/IMC_inf_MED_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,62; 2,38</t>
+          <t>-20,59; 3,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 2,23</t>
+          <t>-22,28; 2,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-33,87; -2,43</t>
+          <t>-34,32; -1,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-35,95; 5,18</t>
+          <t>-34,13; 6,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-39,25; 5,37</t>
+          <t>-38,01; 4,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-57,66; -5,21</t>
+          <t>-61,01; -1,8</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,77; -6,1</t>
+          <t>-24,61; -6,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,53; -10,81</t>
+          <t>-26,47; -10,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,21; -6,78</t>
+          <t>-32,44; -6,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,1; -11,15</t>
+          <t>-40,22; -12,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,53; -25,7</t>
+          <t>-53,51; -25,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,63; -16,22</t>
+          <t>-59,67; -15,67</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 6,11</t>
+          <t>-15,4; 4,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 8,19</t>
+          <t>-11,05; 9,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 9,06</t>
+          <t>-31,28; 8,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 14,16</t>
+          <t>-28,73; 10,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 26,72</t>
+          <t>-28,3; 32,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-75,8; 28,96</t>
+          <t>-74,04; 26,52</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 7,62</t>
+          <t>-13,65; 6,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 0,57</t>
+          <t>-19,54; 0,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 11,05</t>
+          <t>-15,64; 11,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,23; 16,99</t>
+          <t>-24,45; 13,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,96; 1,95</t>
+          <t>-36,79; 2,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,49; 42,74</t>
+          <t>-40,47; 48,38</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,05; -4,07</t>
+          <t>-13,83; -3,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,38; -5,62</t>
+          <t>-15,46; -5,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,25; -4,79</t>
+          <t>-22,81; -4,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,96; -7,88</t>
+          <t>-24,72; -6,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,25; -13,07</t>
+          <t>-32,46; -13,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,09; -13,85</t>
+          <t>-54,39; -13,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_MED_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Habitat-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,59; 3,42</t>
+          <t>-21,25; 2,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 2,07</t>
+          <t>-22,19; 2,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,32; -1,5</t>
+          <t>-32,77; -1,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-34,13; 6,26</t>
+          <t>-34,36; 5,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 4,66</t>
+          <t>-39,13; 6,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-61,01; -1,8</t>
+          <t>-58,46; -5,3</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,61; -6,69</t>
+          <t>-24,54; -6,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,47; -10,18</t>
+          <t>-27,48; -10,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,44; -6,92</t>
+          <t>-32,71; -6,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,22; -12,72</t>
+          <t>-40,04; -11,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,51; -25,29</t>
+          <t>-54,5; -24,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,67; -15,67</t>
+          <t>-60,0; -14,68</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 4,64</t>
+          <t>-15,86; 5,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 9,47</t>
+          <t>-11,41; 7,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-31,28; 8,23</t>
+          <t>-31,62; 8,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,73; 10,96</t>
+          <t>-28,97; 12,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 32,4</t>
+          <t>-27,46; 24,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-74,04; 26,52</t>
+          <t>-75,91; 26,89</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 6,19</t>
+          <t>-13,9; 5,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 0,81</t>
+          <t>-18,73; 0,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 11,15</t>
+          <t>-15,49; 11,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 13,38</t>
+          <t>-25,24; 12,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,79; 2,36</t>
+          <t>-35,75; 1,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,47; 48,38</t>
+          <t>-41,79; 45,56</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,83; -3,64</t>
+          <t>-13,42; -3,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,46; -5,62</t>
+          <t>-15,46; -5,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,81; -4,82</t>
+          <t>-22,53; -4,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,72; -6,86</t>
+          <t>-23,66; -7,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,46; -13,35</t>
+          <t>-32,44; -12,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-54,39; -13,64</t>
+          <t>-51,72; -12,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_MED_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Habitat-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-17,46</t>
+          <t>-17,96</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-35,5%</t>
+          <t>-36,85%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,25; 2,52</t>
+          <t>-21,62; 2,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,19; 2,78</t>
+          <t>-23,21; 2,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-32,77; -1,44</t>
+          <t>-35,0; -2,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-34,36; 5,25</t>
+          <t>-35,95; 5,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-39,13; 6,06</t>
+          <t>-39,25; 5,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-58,46; -5,3</t>
+          <t>-59,63; -7,25</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-19,97</t>
+          <t>-20,39</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-41,08%</t>
+          <t>-41,87%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,54; -6,46</t>
+          <t>-24,77; -6,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,48; -10,15</t>
+          <t>-27,53; -10,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,71; -6,3</t>
+          <t>-33,83; -7,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,04; -11,68</t>
+          <t>-40,1; -11,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,5; -24,87</t>
+          <t>-54,53; -25,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,0; -14,68</t>
+          <t>-62,1; -16,63</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-9,51</t>
+          <t>-5,11</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-28,56%</t>
+          <t>-15,57%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 5,37</t>
+          <t>-15,29; 6,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 7,51</t>
+          <t>-11,78; 8,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 8,63</t>
+          <t>-18,83; 9,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,97; 12,01</t>
+          <t>-28,3; 14,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 24,9</t>
+          <t>-28,68; 26,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-75,91; 26,89</t>
+          <t>-48,91; 40,51</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-2,1</t>
+          <t>-5,45</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-6,69%</t>
+          <t>-17,18%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 5,73</t>
+          <t>-13,69; 7,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 0,53</t>
+          <t>-19,1; 0,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 11,23</t>
+          <t>-17,64; 6,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,24; 12,24</t>
+          <t>-25,23; 16,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,75; 1,0</t>
+          <t>-35,96; 1,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,79; 45,56</t>
+          <t>-46,87; 28,08</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-13,31</t>
+          <t>-13,11</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-32,43%</t>
+          <t>-31,92%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,42; -3,61</t>
+          <t>-14,05; -4,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,46; -5,53</t>
+          <t>-15,38; -5,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,53; -4,37</t>
+          <t>-20,59; -6,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,66; -7,08</t>
+          <t>-24,96; -7,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,44; -12,72</t>
+          <t>-32,25; -13,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-51,72; -12,58</t>
+          <t>-45,71; -16,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_MED_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,7 +529,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad (IMC recogido por medición)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-9,61</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-9,76</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-17,96</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-17,04%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-18,94%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-36,85%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-9.613328898814993</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-9.758240163144889</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-17.96459445227752</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-0.1703779552815174</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.1893839850984942</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.3684672621702153</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-21,62; 2,38</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-23,21; 2,23</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-35,0; -2,64</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-35,95; 5,18</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-39,25; 5,37</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-59,63; -7,25</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-21.61921837096381</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-23.20546941802538</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-35.0015264713812</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.3595176576031323</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.3925192943846253</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.5963105696042414</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.37816738897956</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.230067169536455</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-2.641319836430142</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.05178994386622955</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.05369797315864896</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>-0.0724904205100726</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-15,79</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-19,04</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-20,39</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-27,3%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-41,25%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-41,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-24,77; -6,1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-27,53; -10,81</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-33,83; -7,83</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-40,1; -11,15</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-54,53; -25,7</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-62,1; -16,63</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-15.7931941317363</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-19.04129000906397</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-20.39422710726601</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.2729557268101965</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.4124887660053262</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.4187132287657564</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-5,17</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,46</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,11</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-10,43%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-4,13%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-15,57%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-24.77054192448684</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-27.52701038092438</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-33.83089786125415</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.4010364746384724</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5452716542391381</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.620968373214839</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-15,29; 6,11</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-11,78; 8,19</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-18,83; 9,83</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-28,3; 14,16</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-28,68; 26,72</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-48,91; 40,51</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-6.104271914973872</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-10.81282060840746</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-7.832918526090059</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-0.1114740014478688</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.2570129263136111</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.1662784581290126</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +767,243 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-3,27</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-9,23</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-5,45</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-6,46%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-19,08%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-17,18%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-5.165683755312473</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.461756995891689</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-5.110758921892799</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.10429636007258</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.04128436861522257</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.155663112532285</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-13,69; 7,62</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-19,1; 0,57</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-17,64; 6,9</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-25,23; 16,99</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-35,96; 1,95</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-46,87; 28,08</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-15.28906809286074</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-11.77523863683272</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-18.83136894441053</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.283047701551823</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2868240057935077</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4890722062367051</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6.105830372720778</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.188722059849914</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.827533463658783</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.1416208344406467</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.2671920344877086</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.4050548794243581</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-3.269563830947625</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-9.231345631629956</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-5.44988434428022</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.06459279190446544</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1908101187111192</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1718069742353711</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-13.68854776099473</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-19.09941713157766</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-17.64015705257066</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.2523034306125356</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3595736106829694</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4686656500911253</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.619596620109759</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.5684103077562765</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.903780827150404</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.1699022204480003</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.01946211173047618</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.2808420941462316</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-8,65</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-10,57</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-13,11</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-16,1%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-23,31%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-31,92%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-14,05; -4,07</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-15,38; -5,62</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-20,59; -6,23</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-24,96; -7,88</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-32,25; -13,07</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-45,71; -16,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-8.646016862266686</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-10.57482590979102</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-13.11358105237744</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.1610404554092529</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.2331172834798522</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.3191600958763511</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-14.05485157358868</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-15.3838240810823</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-20.59297094299193</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.2495733593773561</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3225077584074911</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.457093758520137</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>-4.067695096038559</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-5.620049701465927</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-6.229699311760297</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-0.07875899032385812</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-0.1306902523445392</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>-0.1605174301198594</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +1012,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_bre/IMC_inf_MED_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Habitat-trans_bre.xlsx
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-9.613328898814993</v>
+        <v>-8.040326013226029</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-9.758240163144889</v>
+        <v>-11.72166876702428</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-17.96459445227752</v>
+        <v>-18.59568370972144</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>-0.1703779552815174</v>
+        <v>-0.1481489070954081</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.1893839850984942</v>
+        <v>-0.2331979020933029</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.3684672621702153</v>
+        <v>-0.367709918798194</v>
       </c>
     </row>
     <row r="5">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-21.61921837096381</v>
+        <v>-19.10394718380478</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-23.20546941802538</v>
+        <v>-22.32242690331178</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-35.0015264713812</v>
+        <v>-33.56497071886494</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>-0.3595176576031323</v>
+        <v>-0.3202620403076067</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.3925192943846253</v>
+        <v>-0.410809472460404</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.5963105696042414</v>
+        <v>-0.5839637474440668</v>
       </c>
     </row>
     <row r="6">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2.37816738897956</v>
+        <v>3.17064085342093</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2.230067169536455</v>
+        <v>-0.286710781488016</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-2.641319836430142</v>
+        <v>-2.413718830611789</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.05178994386622955</v>
+        <v>0.06799474105634605</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.05369797315864896</v>
+        <v>-0.01534281530115645</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-0.0724904205100726</v>
+        <v>-0.05608960097874101</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-15.7931941317363</v>
+        <v>-12.3107207160528</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-19.04129000906397</v>
+        <v>-18.60964071624489</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-20.39422710726601</v>
+        <v>-18.64485574670796</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.2729557268101965</v>
+        <v>-0.2263579684397202</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.4124887660053262</v>
+        <v>-0.4127164243317398</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.4187132287657564</v>
+        <v>-0.3936635509108378</v>
       </c>
     </row>
     <row r="8">
@@ -712,22 +712,22 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-24.77054192448684</v>
+        <v>-20.75203953582454</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-27.52701038092438</v>
+        <v>-26.11350284784955</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-33.83089786125415</v>
+        <v>-31.18655871397042</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.4010364746384724</v>
+        <v>-0.356842986892111</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.5452716542391381</v>
+        <v>-0.5381233034623566</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.620968373214839</v>
+        <v>-0.5785579662520922</v>
       </c>
     </row>
     <row r="9">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-6.104271914973872</v>
+        <v>-4.939431456520967</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>-10.81282060840746</v>
+        <v>-10.70969020870662</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-7.832918526090059</v>
+        <v>-6.299777412233302</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-0.1114740014478688</v>
+        <v>-0.09212715162041284</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.2570129263136111</v>
+        <v>-0.2546285509599731</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.1662784581290126</v>
+        <v>-0.1474985065121683</v>
       </c>
     </row>
     <row r="10">
@@ -768,22 +768,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-5.165683755312473</v>
+        <v>-4.235550859405762</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-1.461756995891689</v>
+        <v>-2.041816794322771</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-5.110758921892799</v>
+        <v>-3.406193305252775</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-0.10429636007258</v>
+        <v>-0.08561451766875385</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.04128436861522257</v>
+        <v>-0.05354938237871991</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.155663112532285</v>
+        <v>-0.1051878481287648</v>
       </c>
     </row>
     <row r="11">
@@ -794,22 +794,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-15.28906809286074</v>
+        <v>-13.91540048990497</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-11.77523863683272</v>
+        <v>-10.60084914399147</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-18.83136894441053</v>
+        <v>-16.69237394626409</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.283047701551823</v>
+        <v>-0.2608672713844696</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.2868240057935077</v>
+        <v>-0.2532123715540975</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.4890722062367051</v>
+        <v>-0.4284966888087644</v>
       </c>
     </row>
     <row r="12">
@@ -820,22 +820,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>6.105830372720778</v>
+        <v>5.170589585797992</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>8.188722059849914</v>
+        <v>7.431147820504537</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>9.827533463658783</v>
+        <v>11.07113749591129</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.1416208344406467</v>
+        <v>0.118941609201747</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.2671920344877086</v>
+        <v>0.2180088301408892</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.4050548794243581</v>
+        <v>0.4346286034841297</v>
       </c>
     </row>
     <row r="13">
@@ -850,22 +850,22 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>-3.269563830947625</v>
+        <v>-3.106449212054158</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>-9.231345631629956</v>
+        <v>-9.437849253686565</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-5.44988434428022</v>
+        <v>-5.683478646483008</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.06459279190446544</v>
+        <v>-0.06278689381821391</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.1908101187111192</v>
+        <v>-0.2011856327257637</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.1718069742353711</v>
+        <v>-0.1751310905988037</v>
       </c>
     </row>
     <row r="14">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>-13.68854776099473</v>
+        <v>-11.98798413261987</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>-19.09941713157766</v>
+        <v>-19.28019129868385</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-17.64015705257066</v>
+        <v>-19.0229048098645</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.2523034306125356</v>
+        <v>-0.2255955758926736</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.3595736106829694</v>
+        <v>-0.3803666072119209</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.4686656500911253</v>
+        <v>-0.4808987805117805</v>
       </c>
     </row>
     <row r="15">
@@ -902,22 +902,22 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>7.619596620109759</v>
+        <v>5.835043762622864</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.5684103077562765</v>
+        <v>-0.52988104847666</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>6.903780827150404</v>
+        <v>6.607041541779145</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.1699022204480003</v>
+        <v>0.1249962954808642</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.01946211173047618</v>
+        <v>-0.01144838973157282</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.2808420941462316</v>
+        <v>0.2729913692492939</v>
       </c>
     </row>
     <row r="16">
@@ -932,22 +932,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-8.646016862266686</v>
+        <v>-7.130798066898336</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-10.57482590979102</v>
+        <v>-10.88127001684109</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-13.11358105237744</v>
+        <v>-12.32099497987068</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-0.1610404554092529</v>
+        <v>-0.1372871967218577</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.2331172834798522</v>
+        <v>-0.2419034241351145</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.3191600958763511</v>
+        <v>-0.3000036730722092</v>
       </c>
     </row>
     <row r="17">
@@ -958,22 +958,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-14.05485157358868</v>
+        <v>-11.55818027409675</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-15.3838240810823</v>
+        <v>-15.66595578458453</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-20.59297094299193</v>
+        <v>-19.56773449867364</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-0.2495733593773561</v>
+        <v>-0.2154209110154637</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.3225077584074911</v>
+        <v>-0.3299600247251513</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.457093758520137</v>
+        <v>-0.433686800202977</v>
       </c>
     </row>
     <row r="18">
@@ -984,22 +984,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>-4.067695096038559</v>
+        <v>-2.246878864561404</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>-5.620049701465927</v>
+        <v>-6.128327594752905</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-6.229699311760297</v>
+        <v>-5.63538401008767</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>-0.07875899032385812</v>
+        <v>-0.04450487681209975</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.1306902523445392</v>
+        <v>-0.1462447275305425</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.1605174301198594</v>
+        <v>-0.13944170009337</v>
       </c>
     </row>
     <row r="19">
